--- a/Assets/GameResources/GameData/Occurrence.xlsx
+++ b/Assets/GameResources/GameData/Occurrence.xlsx
@@ -101,7 +101,8 @@
     <t>1_2</t>
   </si>
   <si>
-    <t>玩家:你好
+    <t>[Action]S1
+玩家:你好
 系统:测试一下
 [Reward]此处为分支
 [选项一]玩家选择了1
@@ -1118,7 +1119,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" ht="196" spans="1:6">
+    <row r="3" ht="210" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>

--- a/Assets/GameResources/GameData/Occurrence.xlsx
+++ b/Assets/GameResources/GameData/Occurrence.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Ch" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>Tag</t>
   </si>
@@ -52,47 +52,13 @@
     <t>1_1</t>
   </si>
   <si>
-    <t>1.png</t>
-  </si>
-  <si>
     <t>gold</t>
   </si>
   <si>
-    <t>测试事件</t>
-  </si>
-  <si>
-    <t>A:你好
-B:测试
-B:测试
-B:测试~
-A:好
-[Branch]S1
-[选项1]
-A:好
-A:好
-A:好
-[Back]选项1
-[选项2]
-B:测试~
-B:测试~
-B:测试~
-B:测试~
-[Back]选项2
-[选项3]
-B:结束啦~
-[End]选项3
-[BranchBack]S1
-[Branch]S3
-[选项1]
-A:好
-[Back]选项1
-[选项2]喵
-B:结束啦~
-[Back]选项2
-[BranchBack]S3
-A:好
-A:好
-B:结束啦~</t>
+    <t>随机事件一</t>
+  </si>
+  <si>
+    <t>系统:事件一</t>
   </si>
   <si>
     <t>0.0.1</t>
@@ -101,20 +67,13 @@
     <t>1_2</t>
   </si>
   <si>
-    <t>[Action]S1
-玩家:你好
-系统:测试一下
-[Reward]此处为分支
-[选项一]玩家选择了1
-玩家:我选了1！
-玩家:我选了1！！
-[Back]选项一
-[选项二]玩家选择了2
-玩家:我选了2~
-[Back]选项二
-[BranchBack]此处为分支
-玩家:你好
-系统:测试一下</t>
+    <t>pink</t>
+  </si>
+  <si>
+    <t>随机事件二</t>
+  </si>
+  <si>
+    <t>系统:事件二</t>
   </si>
 </sst>
 </file>
@@ -745,18 +704,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1073,10 +1038,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="13.4" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.2818181818182" style="1" customWidth="1"/>
-    <col min="5" max="5" width="48.9636363636364" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
+    <col min="2" max="2" width="33.5545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="33.3818181818182" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6818181818182" style="1" customWidth="1"/>
+    <col min="5" max="5" width="42.1454545454545" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.0181818181818" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1099,44 +1065,44 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="409.5" spans="1:6">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="128" customHeight="1" spans="1:6">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" ht="210" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="4">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="E3" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/GameResources/GameData/Occurrence.xlsx
+++ b/Assets/GameResources/GameData/Occurrence.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="17200" windowHeight="6130"/>
   </bookViews>
   <sheets>
     <sheet name="Ch" sheetId="1" r:id="rId1"/>
@@ -55,10 +55,12 @@
     <t>gold</t>
   </si>
   <si>
-    <t>随机事件一</t>
-  </si>
-  <si>
-    <t>系统:事件一</t>
+    <t>格子的事件</t>
+  </si>
+  <si>
+    <t>系统:事件一
+格子:我能随意加剧情！
+系统:好的，你家了剧情</t>
   </si>
   <si>
     <t>0.0.1</t>
